--- a/BAYN GY.xlsx
+++ b/BAYN GY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63562D74-C432-4B23-8937-24127A53AED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2468A9D8-DD0A-40B1-B856-03BE3213BECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18550" yWindow="1180" windowWidth="17850" windowHeight="18760" activeTab="2" xr2:uid="{4F5840C1-5FD8-4A3A-9BFB-E4B596159E87}"/>
+    <workbookView xWindow="1440" yWindow="4690" windowWidth="19050" windowHeight="16100" activeTab="1" xr2:uid="{4F5840C1-5FD8-4A3A-9BFB-E4B596159E87}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="150">
   <si>
     <t>Price EUR</t>
   </si>
@@ -485,6 +485,9 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -1171,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="17">
-        <v>27.86</v>
+        <v>46.17</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
@@ -1198,7 +1201,7 @@
         <v>982.42</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
@@ -1223,7 +1226,7 @@
       </c>
       <c r="J4" s="1">
         <f>+J2*J3</f>
-        <v>27370.2212</v>
+        <v>45358.331400000003</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
@@ -1250,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
@@ -1274,10 +1277,10 @@
         <v>4</v>
       </c>
       <c r="J6" s="1">
-        <v>34255</v>
+        <v>32518</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
@@ -1298,7 +1301,7 @@
       </c>
       <c r="J7" s="1">
         <f>+J4-J5+J6</f>
-        <v>61625.2212</v>
+        <v>77876.331399999995</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
